--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11D56D7-CDE5-4046-9D4C-183AF542E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545BA066-A34E-4197-AA46-C0037E50525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="96">
   <si>
     <t>Stt</t>
   </si>
@@ -281,6 +281,49 @@
   </si>
   <si>
     <t xml:space="preserve">Chi mì omachi, 2 trứng, bánh afc </t>
+  </si>
+  <si>
+    <t>28/01/2026</t>
+  </si>
+  <si>
+    <t>Thu Đức Anh tiền chạy xe</t>
+  </si>
+  <si>
+    <t>Chi bà đi khám lưng</t>
+  </si>
+  <si>
+    <t>Chi đi mua cá 160 + dừa bến tre 26</t>
+  </si>
+  <si>
+    <t>Hôm nay 10h sáng, cô Thanh kêu chuyển 5tr tiền mặt cho bà đi khám lưng</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 27</t>
+  </si>
+  <si>
+    <t>Đã thu 350k của đức anh nên kh thêm vô</t>
+  </si>
+  <si>
+    <t>Tổng tiền đã gửi cho cô Thanh</t>
+  </si>
+  <si>
+    <t>Đã trừ phí giao dịch ra</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 28</t>
+  </si>
+  <si>
+    <t>Thu tiền bác thành 29 500</t>
+  </si>
+  <si>
+    <t>Chi mua đèn cầy nến ly , hoa, 5 loại trái cây
+đồ cúng kiếng</t>
+  </si>
+  <si>
+    <t>Chi mua dừa bến tre 4 trái</t>
   </si>
 </sst>
 </file>
@@ -457,7 +500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -517,6 +560,12 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -540,6 +589,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -823,7 +875,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A4:N55"/>
+  <dimension ref="A4:N74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -838,31 +890,31 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="str">
+      <c r="A5" s="39" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/01/2026 đến ngày 31/01/2026</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
       <c r="L5" s="10">
         <v>46023</v>
       </c>
@@ -871,15 +923,15 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -893,63 +945,63 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33" t="s">
+      <c r="F9" s="37"/>
+      <c r="G9" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="37" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
@@ -1016,7 +1068,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <f t="shared" ref="A14:A49" si="1">A13+1</f>
+        <f t="shared" ref="A14:A67" si="1">A13+1</f>
         <v>3</v>
       </c>
       <c r="B14" s="6">
@@ -1408,7 +1460,7 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" ref="G29:G48" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
+        <f t="shared" ref="G29:G56" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
         <v>9123000</v>
       </c>
       <c r="H29" s="7"/>
@@ -1770,8 +1822,8 @@
       <c r="D44" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7">
+      <c r="E44" s="28"/>
+      <c r="F44" s="25">
         <v>14050000</v>
       </c>
       <c r="G44" s="7">
@@ -1868,11 +1920,11 @@
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7">
-        <v>360000</v>
+        <v>350000</v>
       </c>
       <c r="G48" s="7">
         <f t="shared" si="2"/>
-        <v>5640000</v>
+        <v>5650000</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="3"/>
@@ -1883,105 +1935,450 @@
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B49" s="6"/>
+      <c r="B49" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="7"/>
+      <c r="D49" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="7">
+        <v>350000</v>
+      </c>
       <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
+      <c r="G49" s="7">
+        <f t="shared" si="2"/>
+        <v>6000000</v>
+      </c>
       <c r="H49" s="7"/>
       <c r="I49" s="3"/>
       <c r="J49" s="12"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="6"/>
+    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
+      <c r="D50" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="28"/>
+      <c r="F50" s="25">
+        <v>5000000</v>
+      </c>
+      <c r="G50" s="25">
+        <f t="shared" si="2"/>
+        <v>1000000</v>
+      </c>
       <c r="H50" s="7"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="12"/>
+      <c r="J50" s="33" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="6"/>
+      <c r="A51" s="3">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="D51" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
+      <c r="F51" s="7">
+        <v>186000</v>
+      </c>
+      <c r="G51" s="7">
+        <f t="shared" si="2"/>
+        <v>814000</v>
+      </c>
       <c r="H51" s="7"/>
       <c r="I51" s="3"/>
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="3">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="7"/>
+      <c r="D52" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1710000</v>
+      </c>
       <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
+      <c r="G52" s="7">
+        <f t="shared" si="2"/>
+        <v>2524000</v>
+      </c>
       <c r="H52" s="7"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="12"/>
+      <c r="J52" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+      <c r="A53" s="3">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="C53" s="3"/>
-      <c r="D53" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="5">
-        <f>SUM(E12:E52)</f>
-        <v>62186000</v>
-      </c>
-      <c r="F53" s="5">
-        <f>SUM(F12:F52)</f>
-        <v>61071000</v>
-      </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
+      <c r="D53" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="7">
+        <v>2180000</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7">
+        <f t="shared" si="2"/>
+        <v>4704000</v>
+      </c>
+      <c r="H53" s="7"/>
       <c r="I53" s="3"/>
       <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
+      <c r="A54" s="3">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="19">
-        <f>SUM(H11:H51)</f>
-        <v>1368000</v>
-      </c>
+      <c r="D54" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="7">
+        <v>500000</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7">
+        <f t="shared" si="2"/>
+        <v>5204000</v>
+      </c>
+      <c r="H54" s="7"/>
       <c r="I54" s="3"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="C55" s="3"/>
-      <c r="D55" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5">
-        <f>G11+E53-F53</f>
-        <v>5640000</v>
-      </c>
-      <c r="H55" s="5"/>
+      <c r="D55" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7">
+        <v>358000</v>
+      </c>
+      <c r="G55" s="7">
+        <f t="shared" si="2"/>
+        <v>4846000</v>
+      </c>
+      <c r="H55" s="7"/>
       <c r="I55" s="3"/>
       <c r="J55" s="12"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7">
+        <v>40000</v>
+      </c>
+      <c r="G56" s="7">
+        <f t="shared" si="2"/>
+        <v>4806000</v>
+      </c>
+      <c r="H56" s="7"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="12"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="12"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="12"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="12"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="12"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="12"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="5">
+        <f>SUM(E12:E69)</f>
+        <v>66926000</v>
+      </c>
+      <c r="F70" s="5">
+        <f>SUM(F12:F69)</f>
+        <v>66645000</v>
+      </c>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="19">
+        <f>SUM(H11:H68)</f>
+        <v>1368000</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5">
+        <f>G11+E70-F70</f>
+        <v>4806000</v>
+      </c>
+      <c r="H72" s="5"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D74" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="36">
+        <v>39683000</v>
+      </c>
+      <c r="I74" s="35" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545BA066-A34E-4197-AA46-C0037E50525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCAB817-4E61-4032-AA0E-73DD979571B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="103">
   <si>
     <t>Stt</t>
   </si>
@@ -324,6 +324,27 @@
   </si>
   <si>
     <t>Chi mua dừa bến tre 4 trái</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 29</t>
+  </si>
+  <si>
+    <t>Chi băng keo điện , băng keo trong, rau</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 30</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu tiền điện của xe trắng cỏ </t>
+  </si>
+  <si>
+    <t>Thu tiền cọc xe của bác Liêms</t>
   </si>
 </sst>
 </file>
@@ -566,6 +587,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -589,9 +613,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -890,31 +911,31 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="str">
+      <c r="A5" s="40" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/01/2026 đến ngày 31/01/2026</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
       <c r="L5" s="10">
         <v>46023</v>
       </c>
@@ -923,15 +944,15 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -945,63 +966,63 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37" t="s">
+      <c r="C9" s="38"/>
+      <c r="D9" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37" t="s">
+      <c r="F9" s="38"/>
+      <c r="G9" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="43" t="s">
+      <c r="H9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="38" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="37"/>
+      <c r="D10" s="38"/>
       <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
@@ -1460,7 +1481,7 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" ref="G29:G56" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
+        <f t="shared" ref="G29:G59" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
         <v>9123000</v>
       </c>
       <c r="H29" s="7"/>
@@ -2087,7 +2108,7 @@
         <v>91</v>
       </c>
       <c r="C55" s="3"/>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="37" t="s">
         <v>94</v>
       </c>
       <c r="E55" s="7"/>
@@ -2111,7 +2132,7 @@
         <v>91</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="45" t="s">
+      <c r="D56" s="37" t="s">
         <v>95</v>
       </c>
       <c r="E56" s="7"/>
@@ -2131,12 +2152,21 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B57" s="15"/>
+      <c r="B57" s="15" t="s">
+        <v>96</v>
+      </c>
       <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="7"/>
+      <c r="D57" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2900000</v>
+      </c>
       <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
+      <c r="G57" s="7">
+        <f t="shared" si="2"/>
+        <v>7706000</v>
+      </c>
       <c r="H57" s="7"/>
       <c r="I57" s="3"/>
       <c r="J57" s="12"/>
@@ -2146,12 +2176,21 @@
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B58" s="15"/>
+      <c r="B58" s="15" t="s">
+        <v>96</v>
+      </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
+      <c r="F58" s="7">
+        <v>160000</v>
+      </c>
+      <c r="G58" s="7">
+        <f t="shared" si="2"/>
+        <v>7546000</v>
+      </c>
       <c r="H58" s="7"/>
       <c r="I58" s="3"/>
       <c r="J58" s="12"/>
@@ -2161,12 +2200,21 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B59" s="15"/>
+      <c r="B59" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="7"/>
+      <c r="D59" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E59" s="7">
+        <v>2070000</v>
+      </c>
       <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
+      <c r="G59" s="7">
+        <f t="shared" si="2"/>
+        <v>9616000</v>
+      </c>
       <c r="H59" s="7"/>
       <c r="I59" s="3"/>
       <c r="J59" s="12"/>
@@ -2176,9 +2224,13 @@
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B60" s="15"/>
+      <c r="B60" s="15">
+        <v>46024</v>
+      </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
+      <c r="D60" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -2191,10 +2243,16 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B61" s="15"/>
+      <c r="B61" s="15">
+        <v>46024</v>
+      </c>
       <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="7"/>
+      <c r="D61" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="7">
+        <v>500000</v>
+      </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -2206,10 +2264,16 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B62" s="15"/>
+      <c r="B62" s="15">
+        <v>46024</v>
+      </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="7"/>
+      <c r="D62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E62" s="7">
+        <v>3000000</v>
+      </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -2324,11 +2388,11 @@
       </c>
       <c r="E70" s="5">
         <f>SUM(E12:E69)</f>
-        <v>66926000</v>
+        <v>75396000</v>
       </c>
       <c r="F70" s="5">
         <f>SUM(F12:F69)</f>
-        <v>66645000</v>
+        <v>66805000</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -2363,7 +2427,7 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5">
         <f>G11+E70-F70</f>
-        <v>4806000</v>
+        <v>13116000</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3"/>

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCAB817-4E61-4032-AA0E-73DD979571B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFCA1B4-A525-41BD-B1BF-B09793D0B622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="104">
   <si>
     <t>Stt</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>Thu tiền cọc xe của bác Liêms</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 1 tháng 2</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1484,7 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" ref="G29:G59" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
+        <f t="shared" ref="G29:G63" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
         <v>9123000</v>
       </c>
       <c r="H29" s="7"/>
@@ -2285,10 +2288,16 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B63" s="15"/>
+      <c r="B63" s="15">
+        <v>46055</v>
+      </c>
       <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="7"/>
+      <c r="D63" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E63" s="7">
+        <v>2315000</v>
+      </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -2388,7 +2397,7 @@
       </c>
       <c r="E70" s="5">
         <f>SUM(E12:E69)</f>
-        <v>75396000</v>
+        <v>77711000</v>
       </c>
       <c r="F70" s="5">
         <f>SUM(F12:F69)</f>
@@ -2427,7 +2436,7 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5">
         <f>G11+E70-F70</f>
-        <v>13116000</v>
+        <v>15431000</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3"/>

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFCA1B4-A525-41BD-B1BF-B09793D0B622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB834B2D-D479-479E-844A-1C155E5862C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" ref="G29:G63" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
+        <f t="shared" ref="G29:G59" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
         <v>9123000</v>
       </c>
       <c r="H29" s="7"/>

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -1,40 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB834B2D-D479-479E-844A-1C155E5862C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C368CF2C-466C-44E2-A2C2-7574BD0C988B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thu Chi" sheetId="1" r:id="rId1"/>
+    <sheet name="Thu chi T2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
   <si>
     <t>Stt</t>
   </si>
@@ -341,13 +333,58 @@
     <t>Thu tiền mặt ngày 31</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu tiền điện của xe trắng cỏ </t>
-  </si>
-  <si>
     <t>Thu tiền cọc xe của bác Liêms</t>
   </si>
   <si>
-    <t>Thu tiền mặt ngày 1 tháng 2</t>
+    <t>Tiền mặt còn lại</t>
+  </si>
+  <si>
+    <t>Thu tiền trọng tính ngày 1 của tháng 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi đồ cúng , bẫy chuột,đèn, nến dán chuột, dán ruồi, xịt khử phòng, 5 loại trái cây hoa, cam , xôi cho đức anh, nước ngọt </t>
+  </si>
+  <si>
+    <t>Chi chuyển tiền dư 10% và điện a Hùng</t>
+  </si>
+  <si>
+    <t>Chi phí giao dịch để nạp tiền TK</t>
+  </si>
+  <si>
+    <t>Chi chuyển tiền dư 10% và điện a Nam</t>
+  </si>
+  <si>
+    <t>Chi trả cọc Chung và 10% dư KPI 60 40</t>
+  </si>
+  <si>
+    <t>Chi trả cọc Hoàng Em và 10% dư KPI 60 40</t>
+  </si>
+  <si>
+    <t>Chi trả tiền 10% cho Khánh</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 1</t>
+  </si>
+  <si>
+    <t>Đã thu tiền trọng tính, đưa trước vào đêm khuya ngày 1</t>
+  </si>
+  <si>
+    <t>Thu tiền mặt ngày 2 đức anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi mua nước ngọt cho thợ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi mua khô gà, trứng, giấy ăn, túi đựng rác </t>
+  </si>
+  <si>
+    <t>Thu tiền linh, thạo, liêm ngày 2, còn thiếu Tính</t>
+  </si>
+  <si>
+    <t>Thu tiền điện thằng xe trắng 300</t>
+  </si>
+  <si>
+    <t>Thu tiền ngày 3 của đức anh</t>
   </si>
 </sst>
 </file>
@@ -355,8 +392,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -438,7 +475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,6 +503,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,9 +565,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -534,9 +577,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -553,20 +596,20 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -574,16 +617,16 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -617,6 +660,43 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -900,20 +980,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A4:N74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="7" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="43.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="7" max="8" width="16.44140625" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A4" s="39" t="s">
         <v>22</v>
       </c>
@@ -926,7 +1006,7 @@
       <c r="H4" s="39"/>
       <c r="I4" s="39"/>
     </row>
-    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/01/2026 đến ngày 31/01/2026</v>
@@ -946,7 +1026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
@@ -957,7 +1037,7 @@
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -968,7 +1048,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="42"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
@@ -979,7 +1059,7 @@
       <c r="H8" s="43"/>
       <c r="I8" s="43"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="38"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -1027,7 +1107,7 @@
       <c r="I10" s="38"/>
       <c r="J10" s="38"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1043,7 +1123,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -1066,7 +1146,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <f>A12+1</f>
         <v>2</v>
@@ -1090,7 +1170,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <f t="shared" ref="A14:A67" si="1">A13+1</f>
         <v>3</v>
@@ -1114,7 +1194,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1140,7 +1220,7 @@
       </c>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1164,7 +1244,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1188,7 +1268,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1212,7 +1292,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1236,7 +1316,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1260,7 +1340,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1284,7 +1364,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1312,7 +1392,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1343,7 +1423,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1367,7 +1447,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1391,7 +1471,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1415,7 +1495,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1439,7 +1519,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="12"/>
     </row>
-    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1467,7 +1547,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1491,7 +1571,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1515,7 +1595,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1539,7 +1619,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1563,7 +1643,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="1:10" ht="57.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1588,7 +1668,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1614,7 +1694,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1638,7 +1718,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1662,7 +1742,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1688,7 +1768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1712,7 +1792,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1736,7 +1816,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1760,7 +1840,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1784,7 +1864,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="12"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1808,7 +1888,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="12"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -1834,7 +1914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -1858,7 +1938,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="12"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -1882,7 +1962,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -1906,7 +1986,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="12"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -1930,7 +2010,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -1954,7 +2034,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="12"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -1978,7 +2058,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="12"/>
     </row>
-    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -2004,7 +2084,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -2028,7 +2108,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -2054,7 +2134,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -2078,7 +2158,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -2102,7 +2182,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -2116,17 +2196,17 @@
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7">
-        <v>358000</v>
+        <v>378000</v>
       </c>
       <c r="G55" s="7">
         <f t="shared" si="2"/>
-        <v>4846000</v>
+        <v>4826000</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="3"/>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -2140,17 +2220,17 @@
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="G56" s="7">
         <f t="shared" si="2"/>
-        <v>4806000</v>
+        <v>4766000</v>
       </c>
       <c r="H56" s="7"/>
       <c r="I56" s="3"/>
       <c r="J56" s="12"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -2168,13 +2248,13 @@
       <c r="F57" s="7"/>
       <c r="G57" s="7">
         <f t="shared" si="2"/>
-        <v>7706000</v>
+        <v>7666000</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="3"/>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -2192,13 +2272,13 @@
       </c>
       <c r="G58" s="7">
         <f t="shared" si="2"/>
-        <v>7546000</v>
+        <v>7506000</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="3"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2216,13 +2296,13 @@
       <c r="F59" s="7"/>
       <c r="G59" s="7">
         <f t="shared" si="2"/>
-        <v>9616000</v>
+        <v>9576000</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="3"/>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -2234,14 +2314,16 @@
       <c r="D60" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E60" s="7"/>
+      <c r="E60" s="7">
+        <v>2120000</v>
+      </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="3"/>
       <c r="J60" s="12"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2251,10 +2333,10 @@
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E61" s="7">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -2262,7 +2344,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -2272,7 +2354,7 @@
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E62" s="7">
         <v>3000000</v>
@@ -2283,28 +2365,28 @@
       <c r="I62" s="3"/>
       <c r="J62" s="12"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="B63" s="15">
-        <v>46055</v>
+        <v>46024</v>
       </c>
       <c r="C63" s="3"/>
-      <c r="D63" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E63" s="7">
-        <v>2315000</v>
-      </c>
-      <c r="F63" s="7"/>
+      <c r="D63" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7">
+        <v>875000</v>
+      </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="3"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -2319,7 +2401,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -2334,7 +2416,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2349,7 +2431,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -2364,7 +2446,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3"/>
@@ -2376,7 +2458,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3"/>
@@ -2388,7 +2470,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2397,18 +2479,18 @@
       </c>
       <c r="E70" s="5">
         <f>SUM(E12:E69)</f>
-        <v>77711000</v>
+        <v>77526000</v>
       </c>
       <c r="F70" s="5">
         <f>SUM(F12:F69)</f>
-        <v>66805000</v>
+        <v>67720000</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="3"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2425,7 +2507,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2436,13 +2518,13 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5">
         <f>G11+E70-F70</f>
-        <v>15431000</v>
+        <v>14331000</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D74" s="34" t="s">
         <v>89</v>
       </c>
@@ -2470,4 +2552,1319 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE098660-2C54-435C-A55B-17EC8C764AAD}">
+  <dimension ref="A4:N74"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="43.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="7" max="8" width="16.44140625" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+    </row>
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="40" t="str">
+        <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
+        <v>Từ ngày 01/02/2026 đến ngày 28/02/2026</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="L5" s="10">
+        <v>46054</v>
+      </c>
+      <c r="N5" s="10">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="42"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="38"/>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="38"/>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
+        <v>14331000</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>1</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47">
+        <v>40000</v>
+      </c>
+      <c r="G12" s="47">
+        <f>G11 + IF(E12&lt;&gt;"", E12, 0) - IF(F12&lt;&gt;"", F12, 0)</f>
+        <v>14291000</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="48"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f>A12+1</f>
+        <v>2</v>
+      </c>
+      <c r="B13" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47">
+        <v>627000</v>
+      </c>
+      <c r="G13" s="47">
+        <f t="shared" ref="G13:G24" si="0">G12 + IF(E13&lt;&gt;"", E13, 0) - IF(F13&lt;&gt;"", F13, 0)</f>
+        <v>13664000</v>
+      </c>
+      <c r="H13" s="47"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="48"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" ref="A14:A67" si="1">A13+1</f>
+        <v>3</v>
+      </c>
+      <c r="B14" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47">
+        <v>500000</v>
+      </c>
+      <c r="G14" s="47">
+        <f t="shared" si="0"/>
+        <v>13164000</v>
+      </c>
+      <c r="H14" s="47"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="48"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B15" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47">
+        <v>3212000</v>
+      </c>
+      <c r="G15" s="47">
+        <f t="shared" si="0"/>
+        <v>9952000</v>
+      </c>
+      <c r="H15" s="47"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="48"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B16" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47">
+        <v>3100000</v>
+      </c>
+      <c r="G16" s="47">
+        <f t="shared" si="0"/>
+        <v>6852000</v>
+      </c>
+      <c r="H16" s="47"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="48"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B17" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="47"/>
+      <c r="F17" s="51">
+        <v>37000</v>
+      </c>
+      <c r="G17" s="47">
+        <f t="shared" si="0"/>
+        <v>6815000</v>
+      </c>
+      <c r="H17" s="47"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="48"/>
+    </row>
+    <row r="18" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B18" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="47">
+        <v>1805000</v>
+      </c>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47">
+        <f t="shared" si="0"/>
+        <v>8620000</v>
+      </c>
+      <c r="H18" s="47"/>
+      <c r="I18" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" s="48"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B19" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="47">
+        <v>620000</v>
+      </c>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47">
+        <f t="shared" si="0"/>
+        <v>9240000</v>
+      </c>
+      <c r="H19" s="47"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="48"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B20" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47">
+        <v>40000</v>
+      </c>
+      <c r="G20" s="47">
+        <f t="shared" si="0"/>
+        <v>9200000</v>
+      </c>
+      <c r="H20" s="47"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="48"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B21" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47">
+        <v>230000</v>
+      </c>
+      <c r="G21" s="47">
+        <f t="shared" si="0"/>
+        <v>8970000</v>
+      </c>
+      <c r="H21" s="47"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="48"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B22" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="53">
+        <v>1590000</v>
+      </c>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53">
+        <f t="shared" si="0"/>
+        <v>10560000</v>
+      </c>
+      <c r="H22" s="53"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="14">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B23" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="56">
+        <v>300000</v>
+      </c>
+      <c r="F23" s="56"/>
+      <c r="G23" s="53">
+        <f t="shared" si="0"/>
+        <v>10860000</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="55"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B24" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="47">
+        <v>570000</v>
+      </c>
+      <c r="F24" s="47"/>
+      <c r="G24" s="53">
+        <f t="shared" si="0"/>
+        <v>11430000</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="48"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47" t="str">
+        <f>IF(AND(E25="",F25=""),"", G24 + IF(E25&lt;&gt;"",E25,0) - IF(F25&lt;&gt;"",F25,0))</f>
+        <v/>
+      </c>
+      <c r="H25" s="47"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="48"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47" t="str">
+        <f>IF(AND(E26="",F26=""),"", G25 + IF(E26&lt;&gt;"",E26,0) - IF(F26&lt;&gt;"",F26,0))</f>
+        <v/>
+      </c>
+      <c r="H26" s="47"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="48"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47" t="str">
+        <f>IF(AND(E27="",F27=""),"", G26 + IF(E27&lt;&gt;"",E27,0) - IF(F27&lt;&gt;"",F27,0))</f>
+        <v/>
+      </c>
+      <c r="H27" s="51"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="48"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="47" t="str">
+        <f>IF(AND(E28="",F28=""),"", G27 + IF(E28&lt;&gt;"",E28,0) - IF(F28&lt;&gt;"",F28,0))</f>
+        <v/>
+      </c>
+      <c r="H28" s="47"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="55"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47" t="str">
+        <f t="shared" ref="G29:G59" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
+        <v/>
+      </c>
+      <c r="H29" s="47"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="48"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H30" s="47"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="48"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H31" s="47"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="48"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H32" s="47"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="48"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H33" s="47"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="58"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H34" s="47"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="48"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H35" s="47"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="48"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H36" s="47"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="48"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H37" s="47"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="60"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H38" s="47"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="48"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H39" s="47"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="48"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H40" s="47"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="48"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H41" s="47"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="48"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H42" s="47"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="48"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H43" s="47"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="48"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H44" s="47"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="48"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H45" s="47"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="48"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H46" s="47"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="48"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H47" s="47"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="48"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H48" s="47"/>
+      <c r="I48" s="46"/>
+      <c r="J48" s="48"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H49" s="47"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="48"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H50" s="47"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="62"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H51" s="47"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="48"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H52" s="47"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="48"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H53" s="47"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="48"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H54" s="47"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="48"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H55" s="47"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="48"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H56" s="47"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="48"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H57" s="47"/>
+      <c r="I57" s="46"/>
+      <c r="J57" s="48"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H58" s="47"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="48"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H59" s="47"/>
+      <c r="I59" s="46"/>
+      <c r="J59" s="48"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="48"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="3">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="48"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="48"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="47"/>
+      <c r="G63" s="47"/>
+      <c r="H63" s="47"/>
+      <c r="I63" s="46"/>
+      <c r="J63" s="48"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="47"/>
+      <c r="G64" s="47"/>
+      <c r="H64" s="47"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="48"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="47"/>
+      <c r="G65" s="47"/>
+      <c r="H65" s="47"/>
+      <c r="I65" s="46"/>
+      <c r="J65" s="48"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="47"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="48"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="46"/>
+      <c r="J67" s="48"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="3"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="47"/>
+      <c r="G68" s="47"/>
+      <c r="H68" s="47"/>
+      <c r="I68" s="46"/>
+      <c r="J68" s="48"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="3"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="46"/>
+      <c r="J69" s="48"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="64">
+        <f>SUM(E12:E69)</f>
+        <v>4885000</v>
+      </c>
+      <c r="F70" s="64">
+        <f>SUM(F12:F69)</f>
+        <v>7786000</v>
+      </c>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="48"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5">
+        <f>G11+E70-F70</f>
+        <v>11430000</v>
+      </c>
+      <c r="H72" s="5"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D74" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="36">
+        <v>39683000</v>
+      </c>
+      <c r="I74" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C368CF2C-466C-44E2-A2C2-7574BD0C988B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC323BF-C2D9-4065-8AF0-470E24A5588D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="126">
   <si>
     <t>Stt</t>
   </si>
@@ -385,6 +385,28 @@
   </si>
   <si>
     <t>Thu tiền ngày 3 của đức anh</t>
+  </si>
+  <si>
+    <t>Thu tiền ngày 3 thạo linh liêm</t>
+  </si>
+  <si>
+    <t>Chi gạo , gia vị, đồ dùng hằng ngày</t>
+  </si>
+  <si>
+    <t>Chi nước ngọt cho thợ</t>
+  </si>
+  <si>
+    <t>Chi gửi tiền lại cọc cho bác Liêm + hỗ trợ xăng 50k
+mượn xe bác đi chợ mua đồ</t>
+  </si>
+  <si>
+    <t>Thu tiền ngày 4</t>
+  </si>
+  <si>
+    <t>Thu đức anh 170k ngày 5</t>
+  </si>
+  <si>
+    <t>Chi tiền thuốc cho mấy ông tây và trả lại bông cồn sát trùng, băng gạc cồn đỏ cho bên nhà nghỉ cho nó đỡ nói ra nói vào</t>
   </si>
 </sst>
 </file>
@@ -636,30 +658,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -697,6 +695,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -994,31 +1016,31 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="40" t="str">
+      <c r="A5" s="59" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/01/2026 đến ngày 31/01/2026</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
       <c r="L5" s="10">
         <v>46023</v>
       </c>
@@ -1027,15 +1049,15 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
+      <c r="A6" s="60"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -1049,63 +1071,63 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38" t="s">
+      <c r="F9" s="57"/>
+      <c r="G9" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="57" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+      <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="38"/>
+      <c r="D10" s="57"/>
       <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -2572,31 +2594,31 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="40" t="str">
+      <c r="A5" s="59" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/02/2026 đến ngày 28/02/2026</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
       <c r="L5" s="10">
         <v>46054</v>
       </c>
@@ -2605,15 +2627,15 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
+      <c r="A6" s="60"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2627,63 +2649,63 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38" t="s">
+      <c r="F9" s="57"/>
+      <c r="G9" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="57" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+      <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="38"/>
+      <c r="D10" s="57"/>
       <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -2709,20 +2731,20 @@
         <v>46055</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47">
+      <c r="E12" s="39"/>
+      <c r="F12" s="39">
         <v>40000</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="39">
         <f>G11 + IF(E12&lt;&gt;"", E12, 0) - IF(F12&lt;&gt;"", F12, 0)</f>
         <v>14291000</v>
       </c>
-      <c r="H12" s="47"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="48"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
@@ -2733,20 +2755,20 @@
         <v>46055</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47">
+      <c r="E13" s="39"/>
+      <c r="F13" s="39">
         <v>627000</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="39">
         <f t="shared" ref="G13:G24" si="0">G12 + IF(E13&lt;&gt;"", E13, 0) - IF(F13&lt;&gt;"", F13, 0)</f>
         <v>13664000</v>
       </c>
-      <c r="H13" s="47"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="48"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
@@ -2757,20 +2779,20 @@
         <v>46055</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47">
+      <c r="E14" s="39"/>
+      <c r="F14" s="39">
         <v>500000</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="39">
         <f t="shared" si="0"/>
         <v>13164000</v>
       </c>
-      <c r="H14" s="47"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="48"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
@@ -2781,20 +2803,20 @@
         <v>46055</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47">
+      <c r="E15" s="39"/>
+      <c r="F15" s="39">
         <v>3212000</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="39">
         <f t="shared" si="0"/>
         <v>9952000</v>
       </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="48"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
@@ -2805,20 +2827,20 @@
         <v>46055</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47">
+      <c r="E16" s="39"/>
+      <c r="F16" s="39">
         <v>3100000</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="39">
         <f t="shared" si="0"/>
         <v>6852000</v>
       </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="48"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
@@ -2829,20 +2851,20 @@
         <v>46055</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="51">
+      <c r="E17" s="39"/>
+      <c r="F17" s="43">
         <v>37000</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="39">
         <f t="shared" si="0"/>
         <v>6815000</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="48"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
@@ -2853,22 +2875,22 @@
         <v>46055</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="39">
         <v>1805000</v>
       </c>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47">
+      <c r="F18" s="39"/>
+      <c r="G18" s="39">
         <f t="shared" si="0"/>
         <v>8620000</v>
       </c>
-      <c r="H18" s="47"/>
-      <c r="I18" s="55" t="s">
+      <c r="H18" s="39"/>
+      <c r="I18" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="J18" s="48"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
@@ -2879,20 +2901,20 @@
         <v>46055</v>
       </c>
       <c r="C19" s="3"/>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="39">
         <v>620000</v>
       </c>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47">
+      <c r="F19" s="39"/>
+      <c r="G19" s="39">
         <f t="shared" si="0"/>
         <v>9240000</v>
       </c>
-      <c r="H19" s="47"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="48"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
@@ -2903,20 +2925,20 @@
         <v>46056</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47">
+      <c r="E20" s="39"/>
+      <c r="F20" s="39">
         <v>40000</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="39">
         <f t="shared" si="0"/>
         <v>9200000</v>
       </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="48"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
@@ -2927,20 +2949,20 @@
         <v>46056</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47">
+      <c r="E21" s="39"/>
+      <c r="F21" s="39">
         <v>230000</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G21" s="39">
         <f t="shared" si="0"/>
         <v>8970000</v>
       </c>
-      <c r="H21" s="47"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="48"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
@@ -2951,20 +2973,20 @@
         <v>46056</v>
       </c>
       <c r="C22" s="14"/>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="45">
         <v>1590000</v>
       </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53">
+      <c r="F22" s="45"/>
+      <c r="G22" s="45">
         <f t="shared" si="0"/>
         <v>10560000</v>
       </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="55"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
@@ -2975,20 +2997,20 @@
         <v>46056</v>
       </c>
       <c r="C23" s="14"/>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="56">
+      <c r="E23" s="48">
         <v>300000</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="53">
+      <c r="F23" s="48"/>
+      <c r="G23" s="45">
         <f t="shared" si="0"/>
         <v>10860000</v>
       </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="55"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
@@ -2999,146 +3021,188 @@
         <v>46056</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="39">
         <v>570000</v>
       </c>
-      <c r="F24" s="47"/>
-      <c r="G24" s="53">
+      <c r="F24" s="39"/>
+      <c r="G24" s="45">
         <f t="shared" si="0"/>
         <v>11430000</v>
       </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="48"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="40"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B25" s="15"/>
+      <c r="B25" s="6">
+        <v>46057</v>
+      </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47" t="str">
+      <c r="D25" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="39">
+        <v>1440000</v>
+      </c>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39">
         <f>IF(AND(E25="",F25=""),"", G24 + IF(E25&lt;&gt;"",E25,0) - IF(F25&lt;&gt;"",F25,0))</f>
-        <v/>
-      </c>
-      <c r="H25" s="47"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="48"/>
+        <v>12870000</v>
+      </c>
+      <c r="H25" s="39"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="40"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B26" s="15"/>
+      <c r="B26" s="6">
+        <v>46057</v>
+      </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47" t="str">
+      <c r="D26" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39">
+        <v>253000</v>
+      </c>
+      <c r="G26" s="39">
         <f>IF(AND(E26="",F26=""),"", G25 + IF(E26&lt;&gt;"",E26,0) - IF(F26&lt;&gt;"",F26,0))</f>
-        <v/>
-      </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="48"/>
+        <v>12617000</v>
+      </c>
+      <c r="H26" s="39"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B27" s="15"/>
+      <c r="B27" s="6">
+        <v>46057</v>
+      </c>
       <c r="C27" s="3"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47" t="str">
+      <c r="D27" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39">
+        <v>50000</v>
+      </c>
+      <c r="G27" s="39">
         <f>IF(AND(E27="",F27=""),"", G26 + IF(E27&lt;&gt;"",E27,0) - IF(F27&lt;&gt;"",F27,0))</f>
-        <v/>
-      </c>
-      <c r="H27" s="51"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="48"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>12567000</v>
+      </c>
+      <c r="H27" s="43"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="40"/>
+    </row>
+    <row r="28" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B28" s="15"/>
+      <c r="B28" s="6">
+        <v>46058</v>
+      </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="47" t="str">
+      <c r="D28" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" s="39"/>
+      <c r="F28" s="43">
+        <v>3050000</v>
+      </c>
+      <c r="G28" s="39">
         <f>IF(AND(E28="",F28=""),"", G27 + IF(E28&lt;&gt;"",E28,0) - IF(F28&lt;&gt;"",F28,0))</f>
-        <v/>
-      </c>
-      <c r="H28" s="47"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="55"/>
+        <v>9517000</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="47"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B29" s="15"/>
+      <c r="B29" s="6">
+        <v>46058</v>
+      </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47" t="str">
+      <c r="D29" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="39">
+        <v>1530000</v>
+      </c>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39">
         <f t="shared" ref="G29:G59" si="2">IF(AND(E29="",F29=""),"", G28 + IF(E29&lt;&gt;"",E29,0) - IF(F29&lt;&gt;"",F29,0))</f>
-        <v/>
-      </c>
-      <c r="H29" s="47"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="48"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>11047000</v>
+      </c>
+      <c r="H29" s="39"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="40"/>
+    </row>
+    <row r="30" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B30" s="15"/>
+      <c r="B30" s="6">
+        <v>46058</v>
+      </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H30" s="47"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="48"/>
+      <c r="D30" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39">
+        <v>190000</v>
+      </c>
+      <c r="G30" s="39">
+        <f t="shared" si="2"/>
+        <v>10857000</v>
+      </c>
+      <c r="H30" s="39"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B31" s="15"/>
+      <c r="B31" s="6">
+        <v>46058</v>
+      </c>
       <c r="C31" s="3"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="H31" s="47"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="48"/>
+      <c r="D31" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="39">
+        <v>170000</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39">
+        <f t="shared" si="2"/>
+        <v>11027000</v>
+      </c>
+      <c r="H31" s="39"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="40"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
@@ -3147,16 +3211,16 @@
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47" t="str">
+      <c r="D32" s="41"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H32" s="47"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="48"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="40"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
@@ -3165,16 +3229,16 @@
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="47" t="str">
+      <c r="D33" s="50"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H33" s="47"/>
-      <c r="I33" s="59"/>
-      <c r="J33" s="58"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="50"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
@@ -3183,16 +3247,16 @@
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="51" t="str">
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="43" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H34" s="47"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="48"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="40"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
@@ -3201,16 +3265,16 @@
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47" t="str">
+      <c r="D35" s="41"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H35" s="47"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="48"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="40"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
@@ -3219,16 +3283,16 @@
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47" t="str">
+      <c r="D36" s="41"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H36" s="47"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="48"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="40"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
@@ -3237,16 +3301,16 @@
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47" t="str">
+      <c r="D37" s="41"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H37" s="47"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="60"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
@@ -3255,16 +3319,16 @@
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47" t="str">
+      <c r="D38" s="53"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H38" s="47"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="48"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="40"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
@@ -3273,16 +3337,16 @@
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47" t="str">
+      <c r="D39" s="41"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H39" s="47"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="48"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="40"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
@@ -3291,16 +3355,16 @@
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47" t="str">
+      <c r="D40" s="47"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H40" s="47"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="48"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="40"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
@@ -3309,16 +3373,16 @@
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47" t="str">
+      <c r="D41" s="41"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H41" s="47"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="48"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="40"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
@@ -3327,16 +3391,16 @@
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47" t="str">
+      <c r="D42" s="41"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H42" s="47"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="48"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="40"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
@@ -3345,16 +3409,16 @@
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47" t="str">
+      <c r="D43" s="47"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H43" s="47"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="48"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="40"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
@@ -3363,16 +3427,16 @@
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="47" t="str">
+      <c r="D44" s="50"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H44" s="47"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="48"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="40"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
@@ -3381,16 +3445,16 @@
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47" t="str">
+      <c r="D45" s="38"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H45" s="47"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="48"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="40"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
@@ -3399,16 +3463,16 @@
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47" t="str">
+      <c r="D46" s="41"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H46" s="47"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="48"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="40"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
@@ -3417,16 +3481,16 @@
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47" t="str">
+      <c r="D47" s="41"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H47" s="47"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="48"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="40"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
@@ -3435,16 +3499,16 @@
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47" t="str">
+      <c r="D48" s="38"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H48" s="47"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="48"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="40"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
@@ -3453,16 +3517,16 @@
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47" t="str">
+      <c r="D49" s="38"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H49" s="47"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="48"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="40"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
@@ -3471,16 +3535,16 @@
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51" t="str">
+      <c r="D50" s="42"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H50" s="47"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="62"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="54"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
@@ -3489,16 +3553,16 @@
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47" t="str">
+      <c r="D51" s="38"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H51" s="47"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="48"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="40"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
@@ -3507,16 +3571,16 @@
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47" t="str">
+      <c r="D52" s="41"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H52" s="47"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="48"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="40"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
@@ -3525,16 +3589,16 @@
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47" t="str">
+      <c r="D53" s="41"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H53" s="47"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="48"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="40"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
@@ -3543,16 +3607,16 @@
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47" t="str">
+      <c r="D54" s="41"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H54" s="47"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="48"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="40"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
@@ -3561,16 +3625,16 @@
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47" t="str">
+      <c r="D55" s="55"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H55" s="47"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="48"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="40"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
@@ -3579,16 +3643,16 @@
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="47" t="str">
+      <c r="D56" s="55"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H56" s="47"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="48"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="40"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
@@ -3597,16 +3661,16 @@
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="47" t="str">
+      <c r="D57" s="41"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H57" s="47"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="48"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="40"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
@@ -3615,16 +3679,16 @@
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47" t="str">
+      <c r="D58" s="38"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H58" s="47"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="48"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="40"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
@@ -3633,16 +3697,16 @@
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="47" t="str">
+      <c r="D59" s="41"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H59" s="47"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="48"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="40"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
@@ -3651,13 +3715,13 @@
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="48"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="40"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
@@ -3666,13 +3730,13 @@
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47"/>
-      <c r="H61" s="47"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="48"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="40"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
@@ -3681,13 +3745,13 @@
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="47"/>
-      <c r="G62" s="47"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="48"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="40"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
@@ -3696,13 +3760,13 @@
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="47"/>
-      <c r="G63" s="47"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="48"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="40"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
@@ -3711,13 +3775,13 @@
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="47"/>
-      <c r="G64" s="47"/>
-      <c r="H64" s="47"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="48"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="40"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
@@ -3726,13 +3790,13 @@
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="47"/>
-      <c r="F65" s="47"/>
-      <c r="G65" s="47"/>
-      <c r="H65" s="47"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="48"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="40"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
@@ -3741,13 +3805,13 @@
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="47"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="48"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="40"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
@@ -3756,57 +3820,57 @@
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="48"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="40"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="47"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="48"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="40"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="46"/>
-      <c r="J69" s="48"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="40"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="61" t="s">
+      <c r="D70" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="64">
+      <c r="E70" s="56">
         <f>SUM(E12:E69)</f>
-        <v>4885000</v>
-      </c>
-      <c r="F70" s="64">
+        <v>8025000</v>
+      </c>
+      <c r="F70" s="56">
         <f>SUM(F12:F69)</f>
-        <v>7786000</v>
-      </c>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="48"/>
+        <v>11329000</v>
+      </c>
+      <c r="G70" s="56"/>
+      <c r="H70" s="56"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="40"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
@@ -3833,7 +3897,7 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5">
         <f>G11+E70-F70</f>
-        <v>11430000</v>
+        <v>11027000</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3"/>

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Quản lý thu chi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC323BF-C2D9-4065-8AF0-470E24A5588D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0533489-3900-4570-8446-57114054D0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thu Chi" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -414,8 +423,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -587,7 +596,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -599,9 +608,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -618,20 +627,20 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -639,16 +648,16 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -659,15 +668,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -676,7 +685,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -694,7 +703,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1002,20 +1011,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A4:N74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="2" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="43.109375" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" customWidth="1"/>
-    <col min="7" max="8" width="16.44140625" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
-    <col min="10" max="10" width="34.44140625" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="34.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>22</v>
       </c>
@@ -1028,7 +1037,7 @@
       <c r="H4" s="58"/>
       <c r="I4" s="58"/>
     </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="59" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/01/2026 đến ngày 31/01/2026</v>
@@ -1048,7 +1057,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="60"/>
       <c r="B6" s="60"/>
       <c r="C6" s="60"/>
@@ -1059,7 +1068,7 @@
       <c r="H6" s="60"/>
       <c r="I6" s="60"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1070,7 +1079,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="61"/>
       <c r="B8" s="62"/>
       <c r="C8" s="62"/>
@@ -1081,7 +1090,7 @@
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -1129,7 +1138,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1145,7 +1154,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -1168,7 +1177,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f>A12+1</f>
         <v>2</v>
@@ -1192,7 +1201,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" ref="A14:A67" si="1">A13+1</f>
         <v>3</v>
@@ -1216,7 +1225,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1242,7 +1251,7 @@
       </c>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1266,7 +1275,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1290,7 +1299,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1314,7 +1323,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1338,7 +1347,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1362,7 +1371,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1386,7 +1395,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1414,7 +1423,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1445,7 +1454,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1469,7 +1478,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1493,7 +1502,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1517,7 +1526,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1541,7 +1550,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="12"/>
     </row>
-    <row r="28" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1569,7 +1578,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1593,7 +1602,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1617,7 +1626,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1641,7 +1650,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1665,7 +1674,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1690,7 +1699,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1716,7 +1725,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1740,7 +1749,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1764,7 +1773,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1790,7 +1799,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1814,7 +1823,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1838,7 +1847,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1862,7 +1871,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1886,7 +1895,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="12"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1910,7 +1919,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="12"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -1936,7 +1945,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -1960,7 +1969,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="12"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -1984,7 +1993,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -2008,7 +2017,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="12"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -2032,7 +2041,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -2056,7 +2065,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="12"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -2080,7 +2089,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="12"/>
     </row>
-    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -2106,7 +2115,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -2130,7 +2139,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -2156,7 +2165,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -2180,7 +2189,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -2204,7 +2213,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -2228,7 +2237,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -2252,7 +2261,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="12"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -2276,7 +2285,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -2300,7 +2309,7 @@
       <c r="I58" s="3"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2324,7 +2333,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -2345,7 +2354,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="12"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2366,7 +2375,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -2387,7 +2396,7 @@
       <c r="I62" s="3"/>
       <c r="J62" s="12"/>
     </row>
-    <row r="63" spans="1:10" ht="42" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -2408,7 +2417,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -2423,7 +2432,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -2438,7 +2447,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2453,7 +2462,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -2468,7 +2477,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3"/>
@@ -2480,7 +2489,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3"/>
@@ -2492,7 +2501,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2512,7 +2521,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2529,7 +2538,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2546,7 +2555,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D74" s="34" t="s">
         <v>89</v>
       </c>
@@ -2579,21 +2588,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE098660-2C54-435C-A55B-17EC8C764AAD}">
   <dimension ref="A4:N74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="2" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="43.109375" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" customWidth="1"/>
-    <col min="7" max="8" width="16.44140625" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
-    <col min="10" max="10" width="34.44140625" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="34.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>22</v>
       </c>
@@ -2606,7 +2615,7 @@
       <c r="H4" s="58"/>
       <c r="I4" s="58"/>
     </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="59" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/02/2026 đến ngày 28/02/2026</v>
@@ -2626,7 +2635,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="60"/>
       <c r="B6" s="60"/>
       <c r="C6" s="60"/>
@@ -2637,7 +2646,7 @@
       <c r="H6" s="60"/>
       <c r="I6" s="60"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -2648,7 +2657,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="61"/>
       <c r="B8" s="62"/>
       <c r="C8" s="62"/>
@@ -2659,7 +2668,7 @@
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
         <v>0</v>
       </c>
@@ -2687,7 +2696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -2707,7 +2716,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2723,7 +2732,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -2746,7 +2755,7 @@
       <c r="I12" s="38"/>
       <c r="J12" s="40"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f>A12+1</f>
         <v>2</v>
@@ -2770,7 +2779,7 @@
       <c r="I13" s="38"/>
       <c r="J13" s="40"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" ref="A14:A67" si="1">A13+1</f>
         <v>3</v>
@@ -2794,7 +2803,7 @@
       <c r="I14" s="38"/>
       <c r="J14" s="40"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -2818,7 +2827,7 @@
       <c r="I15" s="42"/>
       <c r="J15" s="40"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -2842,7 +2851,7 @@
       <c r="I16" s="38"/>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2866,7 +2875,7 @@
       <c r="I17" s="38"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2892,7 +2901,7 @@
       </c>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -2916,7 +2925,7 @@
       <c r="I19" s="38"/>
       <c r="J19" s="40"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -2940,7 +2949,7 @@
       <c r="I20" s="38"/>
       <c r="J20" s="40"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2964,7 +2973,7 @@
       <c r="I21" s="38"/>
       <c r="J21" s="40"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2988,7 +2997,7 @@
       <c r="I22" s="46"/>
       <c r="J22" s="47"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3012,7 +3021,7 @@
       <c r="I23" s="49"/>
       <c r="J23" s="47"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -3036,7 +3045,7 @@
       <c r="I24" s="38"/>
       <c r="J24" s="40"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -3060,7 +3069,7 @@
       <c r="I25" s="38"/>
       <c r="J25" s="40"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -3084,7 +3093,7 @@
       <c r="I26" s="38"/>
       <c r="J26" s="40"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -3108,7 +3117,7 @@
       <c r="I27" s="38"/>
       <c r="J27" s="40"/>
     </row>
-    <row r="28" spans="1:10" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -3132,7 +3141,7 @@
       <c r="I28" s="49"/>
       <c r="J28" s="47"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -3156,7 +3165,7 @@
       <c r="I29" s="38"/>
       <c r="J29" s="40"/>
     </row>
-    <row r="30" spans="1:10" ht="42" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -3180,7 +3189,7 @@
       <c r="I30" s="38"/>
       <c r="J30" s="40"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -3204,7 +3213,7 @@
       <c r="I31" s="38"/>
       <c r="J31" s="40"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -3222,7 +3231,7 @@
       <c r="I32" s="38"/>
       <c r="J32" s="40"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -3240,7 +3249,7 @@
       <c r="I33" s="51"/>
       <c r="J33" s="50"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -3258,7 +3267,7 @@
       <c r="I34" s="38"/>
       <c r="J34" s="40"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -3276,7 +3285,7 @@
       <c r="I35" s="38"/>
       <c r="J35" s="40"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -3294,7 +3303,7 @@
       <c r="I36" s="38"/>
       <c r="J36" s="40"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -3312,7 +3321,7 @@
       <c r="I37" s="38"/>
       <c r="J37" s="52"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -3330,7 +3339,7 @@
       <c r="I38" s="38"/>
       <c r="J38" s="40"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -3348,7 +3357,7 @@
       <c r="I39" s="38"/>
       <c r="J39" s="40"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -3366,7 +3375,7 @@
       <c r="I40" s="38"/>
       <c r="J40" s="40"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -3384,7 +3393,7 @@
       <c r="I41" s="38"/>
       <c r="J41" s="40"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -3402,7 +3411,7 @@
       <c r="I42" s="38"/>
       <c r="J42" s="40"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -3420,7 +3429,7 @@
       <c r="I43" s="38"/>
       <c r="J43" s="40"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -3438,7 +3447,7 @@
       <c r="I44" s="38"/>
       <c r="J44" s="40"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -3456,7 +3465,7 @@
       <c r="I45" s="38"/>
       <c r="J45" s="40"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -3474,7 +3483,7 @@
       <c r="I46" s="38"/>
       <c r="J46" s="40"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -3492,7 +3501,7 @@
       <c r="I47" s="38"/>
       <c r="J47" s="40"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -3510,7 +3519,7 @@
       <c r="I48" s="38"/>
       <c r="J48" s="40"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -3528,7 +3537,7 @@
       <c r="I49" s="38"/>
       <c r="J49" s="40"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -3546,7 +3555,7 @@
       <c r="I50" s="38"/>
       <c r="J50" s="54"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -3564,7 +3573,7 @@
       <c r="I51" s="38"/>
       <c r="J51" s="40"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -3582,7 +3591,7 @@
       <c r="I52" s="38"/>
       <c r="J52" s="40"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -3600,7 +3609,7 @@
       <c r="I53" s="38"/>
       <c r="J53" s="40"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -3618,7 +3627,7 @@
       <c r="I54" s="38"/>
       <c r="J54" s="40"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -3636,7 +3645,7 @@
       <c r="I55" s="38"/>
       <c r="J55" s="40"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -3654,7 +3663,7 @@
       <c r="I56" s="38"/>
       <c r="J56" s="40"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -3672,7 +3681,7 @@
       <c r="I57" s="38"/>
       <c r="J57" s="40"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -3690,7 +3699,7 @@
       <c r="I58" s="38"/>
       <c r="J58" s="40"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -3708,7 +3717,7 @@
       <c r="I59" s="38"/>
       <c r="J59" s="40"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -3723,7 +3732,7 @@
       <c r="I60" s="38"/>
       <c r="J60" s="40"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -3738,7 +3747,7 @@
       <c r="I61" s="38"/>
       <c r="J61" s="40"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -3753,7 +3762,7 @@
       <c r="I62" s="38"/>
       <c r="J62" s="40"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -3768,7 +3777,7 @@
       <c r="I63" s="38"/>
       <c r="J63" s="40"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -3783,7 +3792,7 @@
       <c r="I64" s="38"/>
       <c r="J64" s="40"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -3798,7 +3807,7 @@
       <c r="I65" s="38"/>
       <c r="J65" s="40"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3813,7 +3822,7 @@
       <c r="I66" s="38"/>
       <c r="J66" s="40"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3828,7 +3837,7 @@
       <c r="I67" s="38"/>
       <c r="J67" s="40"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3"/>
@@ -3840,7 +3849,7 @@
       <c r="I68" s="38"/>
       <c r="J68" s="40"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3"/>
@@ -3852,7 +3861,7 @@
       <c r="I69" s="38"/>
       <c r="J69" s="40"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3872,7 +3881,7 @@
       <c r="I70" s="38"/>
       <c r="J70" s="40"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3886,7 +3895,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3903,7 +3912,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D74" s="34" t="s">
         <v>89</v>
       </c>

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Quản lý thu chi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0533489-3900-4570-8446-57114054D0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1856B754-77A0-40CF-BF23-46C15990FF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thu Chi" sheetId="1" r:id="rId1"/>
@@ -21,21 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="134">
   <si>
     <t>Stt</t>
   </si>
@@ -416,6 +407,30 @@
   </si>
   <si>
     <t>Chi tiền thuốc cho mấy ông tây và trả lại bông cồn sát trùng, băng gạc cồn đỏ cho bên nhà nghỉ cho nó đỡ nói ra nói vào</t>
+  </si>
+  <si>
+    <t>Thu tiền ngày 5</t>
+  </si>
+  <si>
+    <t>Chi mua bình ga 20kg màu xanh (bà bán bình ga đc 150k, gửi 150k cho bà)</t>
+  </si>
+  <si>
+    <t>Chi mua sườn và thịt cho bà</t>
+  </si>
+  <si>
+    <t>Chi mua đồ cho anh quyết và dừa cho anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi tiền cọc cho anh Thanh </t>
+  </si>
+  <si>
+    <t>Thu tiền ngày 6</t>
+  </si>
+  <si>
+    <t>Thu 200 tiền điện của xe trắng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 1tr doanh thu đức anh </t>
   </si>
 </sst>
 </file>
@@ -423,8 +438,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -596,7 +611,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -608,9 +623,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -627,20 +642,20 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -648,16 +663,16 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -668,15 +683,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -685,7 +700,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -703,7 +718,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1011,20 +1026,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A4:N74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="7" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="43.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="7" max="8" width="16.44140625" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A4" s="58" t="s">
         <v>22</v>
       </c>
@@ -1037,7 +1052,7 @@
       <c r="H4" s="58"/>
       <c r="I4" s="58"/>
     </row>
-    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="59" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/01/2026 đến ngày 31/01/2026</v>
@@ -1057,7 +1072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="60"/>
       <c r="C6" s="60"/>
@@ -1068,7 +1083,7 @@
       <c r="H6" s="60"/>
       <c r="I6" s="60"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1079,7 +1094,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="61"/>
       <c r="B8" s="62"/>
       <c r="C8" s="62"/>
@@ -1090,7 +1105,7 @@
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="57" t="s">
         <v>0</v>
       </c>
@@ -1118,7 +1133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -1138,7 +1153,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1154,7 +1169,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -1177,7 +1192,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <f>A12+1</f>
         <v>2</v>
@@ -1201,7 +1216,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <f t="shared" ref="A14:A67" si="1">A13+1</f>
         <v>3</v>
@@ -1225,7 +1240,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1251,7 +1266,7 @@
       </c>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1275,7 +1290,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1299,7 +1314,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1323,7 +1338,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1347,7 +1362,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1371,7 +1386,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1395,7 +1410,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1423,7 +1438,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1454,7 +1469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1478,7 +1493,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1502,7 +1517,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1526,7 +1541,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1550,7 +1565,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="12"/>
     </row>
-    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1578,7 +1593,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1602,7 +1617,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1626,7 +1641,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1650,7 +1665,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1674,7 +1689,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="1:10" ht="57.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1699,7 +1714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1725,7 +1740,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1749,7 +1764,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1773,7 +1788,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1799,7 +1814,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1823,7 +1838,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1847,7 +1862,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1871,7 +1886,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1895,7 +1910,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="12"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1919,7 +1934,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="12"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -1945,7 +1960,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -1969,7 +1984,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="12"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -1993,7 +2008,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -2017,7 +2032,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="12"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -2041,7 +2056,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -2065,7 +2080,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="12"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -2089,7 +2104,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="12"/>
     </row>
-    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -2115,7 +2130,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -2139,7 +2154,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -2165,7 +2180,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -2189,7 +2204,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -2213,7 +2228,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -2237,7 +2252,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -2261,7 +2276,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="12"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -2285,7 +2300,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -2309,7 +2324,7 @@
       <c r="I58" s="3"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2333,7 +2348,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -2354,7 +2369,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="12"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2375,7 +2390,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -2396,7 +2411,7 @@
       <c r="I62" s="3"/>
       <c r="J62" s="12"/>
     </row>
-    <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -2417,7 +2432,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -2432,7 +2447,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -2447,7 +2462,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2462,7 +2477,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -2477,7 +2492,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3"/>
@@ -2489,7 +2504,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3"/>
@@ -2501,7 +2516,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2521,7 +2536,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2538,7 +2553,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2555,7 +2570,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D74" s="34" t="s">
         <v>89</v>
       </c>
@@ -2588,21 +2603,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE098660-2C54-435C-A55B-17EC8C764AAD}">
   <dimension ref="A4:N74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="7" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="43.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="7" max="8" width="16.44140625" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A4" s="58" t="s">
         <v>22</v>
       </c>
@@ -2615,7 +2630,7 @@
       <c r="H4" s="58"/>
       <c r="I4" s="58"/>
     </row>
-    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="59" t="str">
         <f>"Từ ngày " &amp; TEXT(L5,"dd/mm/yyyy") &amp; " đến ngày " &amp; TEXT(N5,"dd/mm/yyyy")</f>
         <v>Từ ngày 01/02/2026 đến ngày 28/02/2026</v>
@@ -2635,7 +2650,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="60"/>
       <c r="C6" s="60"/>
@@ -2646,7 +2661,7 @@
       <c r="H6" s="60"/>
       <c r="I6" s="60"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -2657,7 +2672,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="61"/>
       <c r="B8" s="62"/>
       <c r="C8" s="62"/>
@@ -2668,7 +2683,7 @@
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="57" t="s">
         <v>0</v>
       </c>
@@ -2696,7 +2711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="57"/>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -2716,7 +2731,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2732,7 +2747,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -2755,7 +2770,7 @@
       <c r="I12" s="38"/>
       <c r="J12" s="40"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <f>A12+1</f>
         <v>2</v>
@@ -2779,7 +2794,7 @@
       <c r="I13" s="38"/>
       <c r="J13" s="40"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <f t="shared" ref="A14:A67" si="1">A13+1</f>
         <v>3</v>
@@ -2803,7 +2818,7 @@
       <c r="I14" s="38"/>
       <c r="J14" s="40"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -2827,7 +2842,7 @@
       <c r="I15" s="42"/>
       <c r="J15" s="40"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -2851,7 +2866,7 @@
       <c r="I16" s="38"/>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2875,7 +2890,7 @@
       <c r="I17" s="38"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2901,7 +2916,7 @@
       </c>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -2925,7 +2940,7 @@
       <c r="I19" s="38"/>
       <c r="J19" s="40"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -2949,7 +2964,7 @@
       <c r="I20" s="38"/>
       <c r="J20" s="40"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2973,7 +2988,7 @@
       <c r="I21" s="38"/>
       <c r="J21" s="40"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2997,7 +3012,7 @@
       <c r="I22" s="46"/>
       <c r="J22" s="47"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3021,7 +3036,7 @@
       <c r="I23" s="49"/>
       <c r="J23" s="47"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -3045,7 +3060,7 @@
       <c r="I24" s="38"/>
       <c r="J24" s="40"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -3069,7 +3084,7 @@
       <c r="I25" s="38"/>
       <c r="J25" s="40"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -3093,7 +3108,7 @@
       <c r="I26" s="38"/>
       <c r="J26" s="40"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -3117,7 +3132,7 @@
       <c r="I27" s="38"/>
       <c r="J27" s="40"/>
     </row>
-    <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -3141,7 +3156,7 @@
       <c r="I28" s="49"/>
       <c r="J28" s="47"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -3165,7 +3180,7 @@
       <c r="I29" s="38"/>
       <c r="J29" s="40"/>
     </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="42" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -3189,7 +3204,7 @@
       <c r="I30" s="38"/>
       <c r="J30" s="40"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -3213,151 +3228,199 @@
       <c r="I31" s="38"/>
       <c r="J31" s="40"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B32" s="15"/>
+      <c r="B32" s="6">
+        <v>46059</v>
+      </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="39"/>
+      <c r="D32" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="39">
+        <v>1350000</v>
+      </c>
       <c r="F32" s="39"/>
-      <c r="G32" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G32" s="39">
+        <f t="shared" si="2"/>
+        <v>12377000</v>
       </c>
       <c r="H32" s="39"/>
       <c r="I32" s="38"/>
       <c r="J32" s="40"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B33" s="23"/>
+      <c r="B33" s="6">
+        <v>46059</v>
+      </c>
       <c r="C33" s="3"/>
-      <c r="D33" s="50"/>
+      <c r="D33" s="50" t="s">
+        <v>127</v>
+      </c>
       <c r="E33" s="39"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F33" s="43">
+        <v>660000</v>
+      </c>
+      <c r="G33" s="39">
+        <f t="shared" si="2"/>
+        <v>11717000</v>
       </c>
       <c r="H33" s="39"/>
       <c r="I33" s="51"/>
       <c r="J33" s="50"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B34" s="15"/>
+      <c r="B34" s="6">
+        <v>46059</v>
+      </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="38"/>
+      <c r="D34" s="38" t="s">
+        <v>128</v>
+      </c>
       <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F34" s="39">
+        <v>453000</v>
+      </c>
+      <c r="G34" s="43">
+        <f t="shared" si="2"/>
+        <v>11264000</v>
       </c>
       <c r="H34" s="39"/>
       <c r="I34" s="38"/>
       <c r="J34" s="40"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B35" s="15"/>
+      <c r="B35" s="6">
+        <v>46059</v>
+      </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="41"/>
+      <c r="D35" s="41" t="s">
+        <v>129</v>
+      </c>
       <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F35" s="39">
+        <v>360000</v>
+      </c>
+      <c r="G35" s="39">
+        <f t="shared" si="2"/>
+        <v>10904000</v>
       </c>
       <c r="H35" s="39"/>
       <c r="I35" s="38"/>
       <c r="J35" s="40"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B36" s="15"/>
+      <c r="B36" s="6">
+        <v>46060</v>
+      </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="41"/>
+      <c r="D36" s="41" t="s">
+        <v>130</v>
+      </c>
       <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F36" s="39">
+        <v>2600000</v>
+      </c>
+      <c r="G36" s="39">
+        <f t="shared" si="2"/>
+        <v>8304000</v>
       </c>
       <c r="H36" s="39"/>
       <c r="I36" s="38"/>
       <c r="J36" s="40"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B37" s="15"/>
+      <c r="B37" s="6">
+        <v>46060</v>
+      </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="39"/>
+      <c r="D37" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="39">
+        <v>1915000</v>
+      </c>
       <c r="F37" s="39"/>
-      <c r="G37" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G37" s="39">
+        <f t="shared" si="2"/>
+        <v>10219000</v>
       </c>
       <c r="H37" s="39"/>
       <c r="I37" s="38"/>
       <c r="J37" s="52"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B38" s="15"/>
+      <c r="B38" s="6">
+        <v>46060</v>
+      </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="39"/>
+      <c r="D38" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="39">
+        <v>200000</v>
+      </c>
       <c r="F38" s="39"/>
-      <c r="G38" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G38" s="39">
+        <f t="shared" si="2"/>
+        <v>10419000</v>
       </c>
       <c r="H38" s="39"/>
       <c r="I38" s="38"/>
       <c r="J38" s="40"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B39" s="15"/>
+      <c r="B39" s="6">
+        <v>46060</v>
+      </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="39"/>
+      <c r="D39" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="39">
+        <v>1000000</v>
+      </c>
       <c r="F39" s="39"/>
-      <c r="G39" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G39" s="39">
+        <f t="shared" si="2"/>
+        <v>11419000</v>
       </c>
       <c r="H39" s="39"/>
       <c r="I39" s="38"/>
       <c r="J39" s="40"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -3375,7 +3438,7 @@
       <c r="I40" s="38"/>
       <c r="J40" s="40"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -3393,7 +3456,7 @@
       <c r="I41" s="38"/>
       <c r="J41" s="40"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -3410,8 +3473,11 @@
       <c r="H42" s="39"/>
       <c r="I42" s="38"/>
       <c r="J42" s="40"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L42">
+        <v>11804</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -3429,7 +3495,7 @@
       <c r="I43" s="38"/>
       <c r="J43" s="40"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -3447,7 +3513,7 @@
       <c r="I44" s="38"/>
       <c r="J44" s="40"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -3465,7 +3531,7 @@
       <c r="I45" s="38"/>
       <c r="J45" s="40"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -3483,7 +3549,7 @@
       <c r="I46" s="38"/>
       <c r="J46" s="40"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -3501,7 +3567,7 @@
       <c r="I47" s="38"/>
       <c r="J47" s="40"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -3519,7 +3585,7 @@
       <c r="I48" s="38"/>
       <c r="J48" s="40"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -3537,7 +3603,7 @@
       <c r="I49" s="38"/>
       <c r="J49" s="40"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -3547,7 +3613,7 @@
       <c r="D50" s="42"/>
       <c r="E50" s="39"/>
       <c r="F50" s="43"/>
-      <c r="G50" s="43" t="str">
+      <c r="G50" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -3555,7 +3621,7 @@
       <c r="I50" s="38"/>
       <c r="J50" s="54"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -3573,7 +3639,7 @@
       <c r="I51" s="38"/>
       <c r="J51" s="40"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -3591,7 +3657,7 @@
       <c r="I52" s="38"/>
       <c r="J52" s="40"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -3609,7 +3675,7 @@
       <c r="I53" s="38"/>
       <c r="J53" s="40"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -3627,7 +3693,7 @@
       <c r="I54" s="38"/>
       <c r="J54" s="40"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -3645,7 +3711,7 @@
       <c r="I55" s="38"/>
       <c r="J55" s="40"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -3663,7 +3729,7 @@
       <c r="I56" s="38"/>
       <c r="J56" s="40"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -3681,7 +3747,7 @@
       <c r="I57" s="38"/>
       <c r="J57" s="40"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -3699,7 +3765,7 @@
       <c r="I58" s="38"/>
       <c r="J58" s="40"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -3717,7 +3783,7 @@
       <c r="I59" s="38"/>
       <c r="J59" s="40"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -3732,7 +3798,7 @@
       <c r="I60" s="38"/>
       <c r="J60" s="40"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -3747,7 +3813,7 @@
       <c r="I61" s="38"/>
       <c r="J61" s="40"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -3762,7 +3828,7 @@
       <c r="I62" s="38"/>
       <c r="J62" s="40"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -3777,7 +3843,7 @@
       <c r="I63" s="38"/>
       <c r="J63" s="40"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -3792,7 +3858,7 @@
       <c r="I64" s="38"/>
       <c r="J64" s="40"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -3807,7 +3873,7 @@
       <c r="I65" s="38"/>
       <c r="J65" s="40"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3822,7 +3888,7 @@
       <c r="I66" s="38"/>
       <c r="J66" s="40"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3837,7 +3903,7 @@
       <c r="I67" s="38"/>
       <c r="J67" s="40"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="6"/>
       <c r="C68" s="3"/>
@@ -3849,7 +3915,7 @@
       <c r="I68" s="38"/>
       <c r="J68" s="40"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="6"/>
       <c r="C69" s="3"/>
@@ -3861,7 +3927,7 @@
       <c r="I69" s="38"/>
       <c r="J69" s="40"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3870,18 +3936,18 @@
       </c>
       <c r="E70" s="56">
         <f>SUM(E12:E69)</f>
-        <v>8025000</v>
+        <v>12490000</v>
       </c>
       <c r="F70" s="56">
         <f>SUM(F12:F69)</f>
-        <v>11329000</v>
+        <v>15402000</v>
       </c>
       <c r="G70" s="56"/>
       <c r="H70" s="56"/>
       <c r="I70" s="38"/>
       <c r="J70" s="40"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3895,7 +3961,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3906,13 +3972,13 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5">
         <f>G11+E70-F70</f>
-        <v>11027000</v>
+        <v>11419000</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D74" s="34" t="s">
         <v>89</v>
       </c>

--- a/Quản lý thu chi/Thu chi tháng 1.xlsx
+++ b/Quản lý thu chi/Thu chi tháng 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Quản lý thu chi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1856B754-77A0-40CF-BF23-46C15990FF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A93505-3ABA-4C1A-B9A5-28826F9782F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="141">
   <si>
     <t>Stt</t>
   </si>
@@ -431,6 +431,27 @@
   </si>
   <si>
     <t xml:space="preserve">Thu 1tr doanh thu đức anh </t>
+  </si>
+  <si>
+    <t>Thu tiền ngày 7 thạo linh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi tiền đồ, cơm với nước cho anh ru ru </t>
+  </si>
+  <si>
+    <t xml:space="preserve">thu tiền đức anh ngày 8 </t>
+  </si>
+  <si>
+    <t>Thu tiền thạo ngày 8</t>
+  </si>
+  <si>
+    <t>Chi tổng tiền đi chợ cho bà mua sắm vật tư cúng bái tiễn ông công ông táo và mua lương thực dự trữ là 1 triệu</t>
+  </si>
+  <si>
+    <t>Thu tiền đức anh ngày 9</t>
+  </si>
+  <si>
+    <t>Thu tiền back lại tiền chợ từ bà</t>
   </si>
 </sst>
 </file>
@@ -3425,14 +3446,20 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B40" s="15"/>
+      <c r="B40" s="6">
+        <v>46061</v>
+      </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="39"/>
+      <c r="D40" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E40" s="39">
+        <v>1360000</v>
+      </c>
       <c r="F40" s="39"/>
-      <c r="G40" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G40" s="39">
+        <f t="shared" si="2"/>
+        <v>12779000</v>
       </c>
       <c r="H40" s="39"/>
       <c r="I40" s="38"/>
@@ -3443,14 +3470,20 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B41" s="15"/>
+      <c r="B41" s="6">
+        <v>46061</v>
+      </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="41"/>
+      <c r="D41" s="41" t="s">
+        <v>135</v>
+      </c>
       <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F41" s="39">
+        <v>310000</v>
+      </c>
+      <c r="G41" s="39">
+        <f t="shared" si="2"/>
+        <v>12469000</v>
       </c>
       <c r="H41" s="39"/>
       <c r="I41" s="38"/>
@@ -3461,14 +3494,20 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B42" s="15"/>
+      <c r="B42" s="6">
+        <v>46061</v>
+      </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="39"/>
+      <c r="D42" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" s="39">
+        <v>610000</v>
+      </c>
       <c r="F42" s="39"/>
-      <c r="G42" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G42" s="39">
+        <f t="shared" si="2"/>
+        <v>13079000</v>
       </c>
       <c r="H42" s="39"/>
       <c r="I42" s="38"/>
@@ -3482,32 +3521,44 @@
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B43" s="15"/>
+      <c r="B43" s="6">
+        <v>46061</v>
+      </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="39"/>
+      <c r="D43" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" s="39">
+        <v>840000</v>
+      </c>
       <c r="F43" s="39"/>
-      <c r="G43" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G43" s="39">
+        <f t="shared" si="2"/>
+        <v>13919000</v>
       </c>
       <c r="H43" s="39"/>
       <c r="I43" s="38"/>
       <c r="J43" s="40"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B44" s="15"/>
+      <c r="B44" s="6">
+        <v>46062</v>
+      </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="50"/>
+      <c r="D44" s="50" t="s">
+        <v>138</v>
+      </c>
       <c r="E44" s="39"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F44" s="43">
+        <v>1000000</v>
+      </c>
+      <c r="G44" s="39">
+        <f t="shared" si="2"/>
+        <v>12919000</v>
       </c>
       <c r="H44" s="39"/>
       <c r="I44" s="38"/>
@@ -3518,14 +3569,20 @@
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B45" s="15"/>
+      <c r="B45" s="6">
+        <v>46062</v>
+      </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="39"/>
+      <c r="D45" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="E45" s="39">
+        <v>550000</v>
+      </c>
       <c r="F45" s="39"/>
-      <c r="G45" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G45" s="39">
+        <f t="shared" si="2"/>
+        <v>13469000</v>
       </c>
       <c r="H45" s="39"/>
       <c r="I45" s="38"/>
@@ -3536,14 +3593,20 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B46" s="15"/>
+      <c r="B46" s="6">
+        <v>46062</v>
+      </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="39"/>
+      <c r="D46" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" s="39">
+        <v>135000</v>
+      </c>
       <c r="F46" s="39"/>
-      <c r="G46" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G46" s="39">
+        <f t="shared" si="2"/>
+        <v>13604000</v>
       </c>
       <c r="H46" s="39"/>
       <c r="I46" s="38"/>
@@ -3936,11 +3999,11 @@
       </c>
       <c r="E70" s="56">
         <f>SUM(E12:E69)</f>
-        <v>12490000</v>
+        <v>15985000</v>
       </c>
       <c r="F70" s="56">
         <f>SUM(F12:F69)</f>
-        <v>15402000</v>
+        <v>16712000</v>
       </c>
       <c r="G70" s="56"/>
       <c r="H70" s="56"/>
@@ -3972,7 +4035,7 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5">
         <f>G11+E70-F70</f>
-        <v>11419000</v>
+        <v>13604000</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="3"/>
